--- a/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,13 +396,35 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9835</v>
+        <v>1604</v>
       </c>
       <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>4</v>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1604</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1604</v>
+      </c>
+      <c r="B4">
+        <v>68</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,35 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>1604</v>
+        <v>25899</v>
       </c>
       <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
         <v>3</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>1604</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>1604</v>
-      </c>
-      <c r="B4">
-        <v>68</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
@@ -396,13 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>25899</v>
+        <v>9126</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
@@ -396,7 +396,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9126</v>
+        <v>5076</v>
       </c>
       <c r="B2">
         <v>1</v>

--- a/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,13 +396,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>5076</v>
+        <v>394</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>394</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_700.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,24 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>394</v>
+        <v>4927</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>394</v>
-      </c>
-      <c r="B3">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
